--- a/poker/resources/sample/PointsAwardSignin.xlsx
+++ b/poker/resources/sample/PointsAwardSignin.xlsx
@@ -55,12 +55,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+空值：表示默认数据
+有日期：对应月份读取的数据</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>序列ID</t>
   </si>
@@ -71,19 +94,28 @@
     <t>奖励</t>
   </si>
   <si>
+    <t>开启时间</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>day</t>
   </si>
   <si>
-    <t>getitem</t>
+    <t>getItem</t>
+  </si>
+  <si>
+    <t>time</t>
   </si>
   <si>
     <t>1022504_10</t>
@@ -183,11 +215,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -383,7 +416,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -399,6 +432,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -715,7 +760,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -739,16 +784,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -757,89 +802,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -863,14 +908,32 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1212,7 +1275,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
@@ -1222,7 +1285,7 @@
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1232,579 +1295,1031 @@
       <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="C2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="6"/>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
+      <c r="D4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:7">
-      <c r="A5" s="2">
+      <c r="A5" s="11">
         <v>1</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="11">
         <v>0</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:7">
+      <c r="A6" s="11">
+        <v>2</v>
+      </c>
+      <c r="B6" s="11">
+        <v>1</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:7">
+      <c r="A7" s="11">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11">
+        <v>2</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:7">
+      <c r="A8" s="11">
+        <v>4</v>
+      </c>
+      <c r="B8" s="11">
+        <v>3</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:9">
+      <c r="A9" s="11">
+        <v>5</v>
+      </c>
+      <c r="B9" s="11">
+        <v>4</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="14"/>
+      <c r="I9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:9">
+      <c r="A10" s="11">
+        <v>6</v>
+      </c>
+      <c r="B10" s="11">
+        <v>5</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="14"/>
+      <c r="I10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:9">
+      <c r="A11" s="11">
+        <v>7</v>
+      </c>
+      <c r="B11" s="11">
+        <v>6</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
+      <c r="I11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:9">
+      <c r="A12" s="11">
         <v>8</v>
       </c>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:7">
-      <c r="A6" s="2">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="B12" s="11">
+        <v>7</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="12"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="14"/>
+      <c r="I12" s="2"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="11">
         <v>9</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:7">
-      <c r="A7" s="2">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2">
-        <v>2</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B13" s="11">
+        <v>8</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="12"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="I13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="11">
         <v>10</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:7">
-      <c r="A8" s="2">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="B14" s="11">
+        <v>9</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="I14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:9">
+      <c r="A15" s="11">
         <v>11</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:9">
-      <c r="A9" s="2">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2">
-        <v>4</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="10"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:9">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>5</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="10"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:9">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="10"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:9">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="10"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2">
-        <v>8</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="2">
+      <c r="B15" s="11">
         <v>10</v>
       </c>
-      <c r="B14" s="2">
-        <v>9</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:9">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2">
-        <v>10</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
+      <c r="C15" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="12"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="5"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" s="3" customFormat="1" spans="1:9">
-      <c r="A16" s="2">
+      <c r="A16" s="11">
         <v>12</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="11">
         <v>11</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="14"/>
+      <c r="I16" s="2"/>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:9">
+      <c r="A17" s="11">
+        <v>13</v>
+      </c>
+      <c r="B17" s="11">
+        <v>12</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="12"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="14"/>
+      <c r="I17" s="2"/>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:9">
+      <c r="A18" s="11">
+        <v>14</v>
+      </c>
+      <c r="B18" s="11">
+        <v>13</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="14"/>
+      <c r="I18" s="2"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:9">
+      <c r="A19" s="11">
+        <v>15</v>
+      </c>
+      <c r="B19" s="11">
+        <v>14</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="12"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="14"/>
+      <c r="I19" s="2"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:9">
+      <c r="A20" s="11">
+        <v>16</v>
+      </c>
+      <c r="B20" s="11">
+        <v>15</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="12"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="11">
+        <v>17</v>
+      </c>
+      <c r="B21" s="11">
+        <v>16</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="12"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:7">
+      <c r="A22" s="11">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11">
+        <v>17</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" s="12"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:7">
+      <c r="A23" s="11">
         <v>19</v>
       </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="10"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:9">
-      <c r="A17" s="2">
+      <c r="B23" s="11">
+        <v>18</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="12"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:7">
+      <c r="A24" s="11">
+        <v>20</v>
+      </c>
+      <c r="B24" s="11">
+        <v>19</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="12"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="14"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:7">
+      <c r="A25" s="11">
+        <v>21</v>
+      </c>
+      <c r="B25" s="11">
+        <v>20</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="12"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="14"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:7">
+      <c r="A26" s="11">
+        <v>22</v>
+      </c>
+      <c r="B26" s="11">
+        <v>21</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="12"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="11">
+        <v>23</v>
+      </c>
+      <c r="B27" s="11">
+        <v>22</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="12"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+    </row>
+    <row r="28" spans="1:6">
+      <c r="A28" s="11">
+        <v>24</v>
+      </c>
+      <c r="B28" s="11">
+        <v>23</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="12"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="11">
+        <v>25</v>
+      </c>
+      <c r="B29" s="11">
+        <v>24</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="12"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+    </row>
+    <row r="30" spans="1:6">
+      <c r="A30" s="11">
+        <v>26</v>
+      </c>
+      <c r="B30" s="11">
+        <v>25</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="12"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+    </row>
+    <row r="31" spans="1:6">
+      <c r="A31" s="11">
+        <v>27</v>
+      </c>
+      <c r="B31" s="11">
+        <v>26</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D31" s="12"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="11">
+        <v>28</v>
+      </c>
+      <c r="B32" s="11">
+        <v>27</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="12"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="A33" s="11">
+        <v>29</v>
+      </c>
+      <c r="B33" s="11">
+        <v>28</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D33" s="12"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34" s="11">
+        <v>30</v>
+      </c>
+      <c r="B34" s="11">
+        <v>29</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D34" s="12"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="11">
+        <v>31</v>
+      </c>
+      <c r="B35" s="11">
+        <v>30</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D35" s="12"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:7">
+      <c r="A36" s="15">
+        <v>101</v>
+      </c>
+      <c r="B36" s="15">
+        <v>0</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="1:7">
+      <c r="A37" s="15">
+        <v>102</v>
+      </c>
+      <c r="B37" s="15">
+        <v>1</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:7">
+      <c r="A38" s="15">
+        <v>103</v>
+      </c>
+      <c r="B38" s="15">
+        <v>2</v>
+      </c>
+      <c r="C38" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2">
+      <c r="D38" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+    </row>
+    <row r="39" s="2" customFormat="1" spans="1:7">
+      <c r="A39" s="15">
+        <v>104</v>
+      </c>
+      <c r="B39" s="15">
+        <v>3</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+    </row>
+    <row r="40" s="3" customFormat="1" spans="1:9">
+      <c r="A40" s="15">
+        <v>105</v>
+      </c>
+      <c r="B40" s="15">
+        <v>4</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="14"/>
+      <c r="I40" s="2"/>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:9">
+      <c r="A41" s="15">
+        <v>106</v>
+      </c>
+      <c r="B41" s="15">
+        <v>5</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="14"/>
+      <c r="I41" s="2"/>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:9">
+      <c r="A42" s="15">
+        <v>107</v>
+      </c>
+      <c r="B42" s="15">
+        <v>6</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="14"/>
+      <c r="I42" s="2"/>
+    </row>
+    <row r="43" s="3" customFormat="1" spans="1:9">
+      <c r="A43" s="15">
+        <v>108</v>
+      </c>
+      <c r="B43" s="15">
+        <v>7</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="14"/>
+      <c r="I43" s="2"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="15">
+        <v>109</v>
+      </c>
+      <c r="B44" s="15">
+        <v>8</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="I44" s="2"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="15">
+        <v>110</v>
+      </c>
+      <c r="B45" s="15">
+        <v>9</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="I45" s="2"/>
+    </row>
+    <row r="46" customFormat="1" spans="1:9">
+      <c r="A46" s="15">
+        <v>111</v>
+      </c>
+      <c r="B46" s="15">
+        <v>10</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="5"/>
+      <c r="I46" s="2"/>
+    </row>
+    <row r="47" s="3" customFormat="1" spans="1:9">
+      <c r="A47" s="15">
+        <v>112</v>
+      </c>
+      <c r="B47" s="15">
+        <v>11</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="14"/>
+      <c r="I47" s="2"/>
+    </row>
+    <row r="48" s="3" customFormat="1" spans="1:9">
+      <c r="A48" s="15">
+        <v>113</v>
+      </c>
+      <c r="B48" s="15">
         <v>12</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C48" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D48" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="14"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" s="3" customFormat="1" spans="1:9">
+      <c r="A49" s="15">
+        <v>114</v>
+      </c>
+      <c r="B49" s="15">
+        <v>13</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="14"/>
+      <c r="I49" s="2"/>
+    </row>
+    <row r="50" s="3" customFormat="1" spans="1:9">
+      <c r="A50" s="15">
+        <v>115</v>
+      </c>
+      <c r="B50" s="15">
+        <v>14</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="D50" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="14"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:9">
+      <c r="A51" s="15">
+        <v>116</v>
+      </c>
+      <c r="B51" s="15">
+        <v>15</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="D51" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" s="15">
+        <v>117</v>
+      </c>
+      <c r="B52" s="15">
+        <v>16</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52" s="16">
+        <v>45931</v>
+      </c>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:7">
+      <c r="A53" s="15">
+        <v>118</v>
+      </c>
+      <c r="B53" s="15">
+        <v>17</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="14"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:7">
+      <c r="A54" s="15">
+        <v>119</v>
+      </c>
+      <c r="B54" s="15">
+        <v>18</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="14"/>
+    </row>
+    <row r="55" s="3" customFormat="1" spans="1:7">
+      <c r="A55" s="15">
+        <v>120</v>
+      </c>
+      <c r="B55" s="15">
+        <v>19</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="14"/>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:7">
+      <c r="A56" s="15">
+        <v>121</v>
+      </c>
+      <c r="B56" s="15">
         <v>20</v>
       </c>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="10"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:9">
-      <c r="A18" s="2">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2">
-        <v>13</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="C56" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="14"/>
+    </row>
+    <row r="57" s="3" customFormat="1" spans="1:7">
+      <c r="A57" s="15">
+        <v>122</v>
+      </c>
+      <c r="B57" s="15">
         <v>21</v>
       </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:9">
-      <c r="A19" s="2">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2">
-        <v>14</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="C57" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
+    </row>
+    <row r="58" spans="1:6">
+      <c r="A58" s="15">
+        <v>123</v>
+      </c>
+      <c r="B58" s="15">
         <v>22</v>
       </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="10"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:9">
-      <c r="A20" s="2">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
+      <c r="C58" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+    </row>
+    <row r="59" spans="1:6">
+      <c r="A59" s="15">
+        <v>124</v>
+      </c>
+      <c r="B59" s="15">
         <v>23</v>
       </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="2">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2">
-        <v>16</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="C59" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+    </row>
+    <row r="60" spans="1:6">
+      <c r="A60" s="15">
+        <v>125</v>
+      </c>
+      <c r="B60" s="15">
         <v>24</v>
       </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:7">
-      <c r="A22" s="2">
-        <v>18</v>
-      </c>
-      <c r="B22" s="2">
-        <v>17</v>
-      </c>
-      <c r="C22" s="2" t="s">
+      <c r="C60" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="15">
+        <v>126</v>
+      </c>
+      <c r="B61" s="15">
         <v>25</v>
       </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="10"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:7">
-      <c r="A23" s="2">
-        <v>19</v>
-      </c>
-      <c r="B23" s="2">
-        <v>18</v>
-      </c>
-      <c r="C23" s="2" t="s">
+      <c r="C61" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="15">
+        <v>127</v>
+      </c>
+      <c r="B62" s="15">
         <v>26</v>
       </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="10"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:7">
-      <c r="A24" s="2">
-        <v>20</v>
-      </c>
-      <c r="B24" s="2">
-        <v>19</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="C62" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="D62" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="13"/>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="15">
+        <v>128</v>
+      </c>
+      <c r="B63" s="15">
         <v>27</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="10"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:7">
-      <c r="A25" s="2">
-        <v>21</v>
-      </c>
-      <c r="B25" s="2">
-        <v>20</v>
-      </c>
-      <c r="C25" s="2" t="s">
+      <c r="C63" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="13"/>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="15">
+        <v>129</v>
+      </c>
+      <c r="B64" s="15">
         <v>28</v>
       </c>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="10"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:7">
-      <c r="A26" s="2">
-        <v>22</v>
-      </c>
-      <c r="B26" s="2">
-        <v>21</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="C64" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13"/>
+    </row>
+    <row r="65" spans="1:6">
+      <c r="A65" s="15">
+        <v>130</v>
+      </c>
+      <c r="B65" s="15">
         <v>29</v>
       </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2">
-        <v>23</v>
-      </c>
-      <c r="B27" s="2">
-        <v>22</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="C65" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D65" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+    </row>
+    <row r="66" spans="1:6">
+      <c r="A66" s="15">
+        <v>131</v>
+      </c>
+      <c r="B66" s="15">
         <v>30</v>
       </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="2">
-        <v>24</v>
-      </c>
-      <c r="B28" s="2">
-        <v>23</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="2">
-        <v>25</v>
-      </c>
-      <c r="B29" s="2">
-        <v>24</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="2">
-        <v>26</v>
-      </c>
-      <c r="B30" s="2">
-        <v>25</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="2">
-        <v>27</v>
-      </c>
-      <c r="B31" s="2">
-        <v>26</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="2">
-        <v>28</v>
-      </c>
-      <c r="B32" s="2">
-        <v>27</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="2">
-        <v>29</v>
-      </c>
-      <c r="B33" s="2">
-        <v>28</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="2">
-        <v>30</v>
-      </c>
-      <c r="B34" s="2">
-        <v>29</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="2">
-        <v>31</v>
-      </c>
-      <c r="B35" s="2">
-        <v>30</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D35" s="9"/>
-      <c r="E35" s="9"/>
-      <c r="F35" s="9"/>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" spans="2:3">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-    </row>
-    <row r="45" spans="2:3">
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-    </row>
-    <row r="46" spans="3:3">
-      <c r="C46" s="2"/>
-    </row>
-    <row r="47" spans="3:3">
-      <c r="C47" s="2"/>
-    </row>
-    <row r="48" spans="3:3">
-      <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="3:3">
-      <c r="C49" s="2"/>
+      <c r="C66" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="D66" s="16">
+        <v>45931</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/PointsAwardSignin.xlsx
+++ b/poker/resources/sample/PointsAwardSignin.xlsx
@@ -55,7 +55,73 @@
         </r>
       </text>
     </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+最多配置1个道具，但积分就要不配置了，反之一样</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+根据活动结束要清除数据，单独字段配置</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+填写道具Item资源文件夹中的道具名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,7 +149,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="17">
   <si>
     <t>序列ID</t>
   </si>
@@ -91,7 +157,13 @@
     <t>签到天数</t>
   </si>
   <si>
-    <t>奖励</t>
+    <t>道具奖励</t>
+  </si>
+  <si>
+    <t>积分奖励</t>
+  </si>
+  <si>
+    <t>积分ICON</t>
   </si>
   <si>
     <t>开启时间</t>
@@ -115,112 +187,30 @@
     <t>getItem</t>
   </si>
   <si>
+    <t>integralNum</t>
+  </si>
+  <si>
+    <t>integralIcon</t>
+  </si>
+  <si>
     <t>time</t>
   </si>
   <si>
-    <t>1022504_10</t>
+    <t>itemicon_1022504.png</t>
   </si>
   <si>
-    <t>1022504_15</t>
-  </si>
-  <si>
-    <t>1022504_20</t>
-  </si>
-  <si>
-    <t>1022504_25</t>
-  </si>
-  <si>
-    <t>1022504_30</t>
-  </si>
-  <si>
-    <t>1022504_35</t>
-  </si>
-  <si>
-    <t>1022504_40</t>
-  </si>
-  <si>
-    <t>1022504_45</t>
-  </si>
-  <si>
-    <t>1022504_50</t>
-  </si>
-  <si>
-    <t>1022504_55</t>
-  </si>
-  <si>
-    <t>1022504_60</t>
-  </si>
-  <si>
-    <t>1022504_65</t>
-  </si>
-  <si>
-    <t>1022504_70</t>
-  </si>
-  <si>
-    <t>1022504_75</t>
-  </si>
-  <si>
-    <t>1022504_80</t>
-  </si>
-  <si>
-    <t>1022504_85</t>
-  </si>
-  <si>
-    <t>1022504_90</t>
-  </si>
-  <si>
-    <t>1022504_95</t>
-  </si>
-  <si>
-    <t>1022504_100</t>
-  </si>
-  <si>
-    <t>1022504_105</t>
-  </si>
-  <si>
-    <t>1022504_110</t>
-  </si>
-  <si>
-    <t>1022504_115</t>
-  </si>
-  <si>
-    <t>1022504_120</t>
-  </si>
-  <si>
-    <t>1022504_125</t>
-  </si>
-  <si>
-    <t>1022504_130</t>
-  </si>
-  <si>
-    <t>1022504_135</t>
-  </si>
-  <si>
-    <t>1022504_140</t>
-  </si>
-  <si>
-    <t>1022504_145</t>
-  </si>
-  <si>
-    <t>1022504_150</t>
-  </si>
-  <si>
-    <t>1022504_155</t>
-  </si>
-  <si>
-    <t>1022504_160</t>
+    <t>2025/10/01 00:00:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -884,7 +874,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -900,6 +890,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -909,31 +902,46 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1275,1051 +1283,1321 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7" style="4" customWidth="1"/>
     <col min="2" max="2" width="14.75" style="4" customWidth="1"/>
-    <col min="3" max="3" width="16.375" style="4" customWidth="1"/>
-    <col min="4" max="7" width="14.5" style="5" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="4"/>
+    <col min="3" max="4" width="16.375" style="4" customWidth="1"/>
+    <col min="5" max="5" width="23.625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="21.25" style="5" customWidth="1"/>
+    <col min="7" max="9" width="14.5" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="6" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="F1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="11"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:9">
+      <c r="A5" s="16">
+        <v>1</v>
+      </c>
+      <c r="B5" s="16">
+        <v>0</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17">
+        <v>5</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:9">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="17">
+        <v>10</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" s="2" customFormat="1" spans="1:9">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16">
+        <v>2</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17">
+        <v>15</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" s="2" customFormat="1" spans="1:9">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="B8" s="16">
+        <v>3</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="17">
+        <v>20</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" s="3" customFormat="1" spans="1:11">
+      <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="B9" s="16">
+        <v>4</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="17">
+        <v>25</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="22"/>
+      <c r="K9" s="2"/>
+    </row>
+    <row r="10" s="3" customFormat="1" spans="1:11">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="6" t="s">
+      <c r="B10" s="16">
+        <v>5</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="17">
+        <v>30</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="22"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" s="3" customFormat="1" spans="1:11">
+      <c r="A11" s="16">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B11" s="16">
+        <v>6</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="17">
+        <v>35</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="22"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" s="3" customFormat="1" spans="1:11">
+      <c r="A12" s="16">
         <v>8</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="B12" s="16">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="17">
+        <v>40</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="22"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="16">
         <v>9</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="B13" s="16">
+        <v>8</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="17">
+        <v>45</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="K13" s="2"/>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="16">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="8"/>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:7">
-      <c r="A5" s="11">
+      <c r="B14" s="16">
+        <v>9</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="17">
+        <v>50</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" customFormat="1" spans="1:11">
+      <c r="A15" s="16">
+        <v>11</v>
+      </c>
+      <c r="B15" s="16">
+        <v>10</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="17">
+        <v>55</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="6"/>
+      <c r="K15" s="2"/>
+    </row>
+    <row r="16" s="3" customFormat="1" spans="1:11">
+      <c r="A16" s="16">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16">
+        <v>11</v>
+      </c>
+      <c r="C16" s="16"/>
+      <c r="D16" s="17">
+        <v>60</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="22"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" s="3" customFormat="1" spans="1:11">
+      <c r="A17" s="16">
+        <v>13</v>
+      </c>
+      <c r="B17" s="16">
+        <v>12</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="17">
+        <v>65</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="22"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" s="3" customFormat="1" spans="1:11">
+      <c r="A18" s="16">
+        <v>14</v>
+      </c>
+      <c r="B18" s="16">
+        <v>13</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="17">
+        <v>70</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="22"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" s="3" customFormat="1" spans="1:11">
+      <c r="A19" s="16">
+        <v>15</v>
+      </c>
+      <c r="B19" s="16">
+        <v>14</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="17">
+        <v>75</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="22"/>
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" s="3" customFormat="1" spans="1:11">
+      <c r="A20" s="16">
+        <v>16</v>
+      </c>
+      <c r="B20" s="16">
+        <v>15</v>
+      </c>
+      <c r="C20" s="16"/>
+      <c r="D20" s="17">
+        <v>80</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="16">
+        <v>17</v>
+      </c>
+      <c r="B21" s="16">
+        <v>16</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="17">
+        <v>85</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="18"/>
+    </row>
+    <row r="22" s="3" customFormat="1" spans="1:9">
+      <c r="A22" s="16">
+        <v>18</v>
+      </c>
+      <c r="B22" s="16">
+        <v>17</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="17">
+        <v>90</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="22"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:9">
+      <c r="A23" s="16">
+        <v>19</v>
+      </c>
+      <c r="B23" s="16">
+        <v>18</v>
+      </c>
+      <c r="C23" s="16"/>
+      <c r="D23" s="17">
+        <v>95</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="22"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:9">
+      <c r="A24" s="16">
+        <v>20</v>
+      </c>
+      <c r="B24" s="16">
+        <v>19</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="17">
+        <v>100</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="22"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:9">
+      <c r="A25" s="16">
+        <v>21</v>
+      </c>
+      <c r="B25" s="16">
+        <v>20</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="17">
+        <v>105</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="22"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:9">
+      <c r="A26" s="16">
+        <v>22</v>
+      </c>
+      <c r="B26" s="16">
+        <v>21</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="17">
+        <v>110</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="16">
+        <v>23</v>
+      </c>
+      <c r="B27" s="16">
+        <v>22</v>
+      </c>
+      <c r="C27" s="16"/>
+      <c r="D27" s="17">
+        <v>115</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="16">
+        <v>24</v>
+      </c>
+      <c r="B28" s="16">
+        <v>23</v>
+      </c>
+      <c r="C28" s="16"/>
+      <c r="D28" s="17">
+        <v>120</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="16">
+        <v>25</v>
+      </c>
+      <c r="B29" s="16">
+        <v>24</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="17">
+        <v>125</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F29" s="18"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="16">
+        <v>26</v>
+      </c>
+      <c r="B30" s="16">
+        <v>25</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="17">
+        <v>130</v>
+      </c>
+      <c r="E30" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="18"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="16">
+        <v>27</v>
+      </c>
+      <c r="B31" s="16">
+        <v>26</v>
+      </c>
+      <c r="C31" s="16"/>
+      <c r="D31" s="17">
+        <v>135</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="16">
+        <v>28</v>
+      </c>
+      <c r="B32" s="16">
+        <v>27</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="17">
+        <v>140</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="18"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="16">
+        <v>29</v>
+      </c>
+      <c r="B33" s="16">
+        <v>28</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="17">
+        <v>145</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F33" s="18"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="16">
+        <v>30</v>
+      </c>
+      <c r="B34" s="16">
+        <v>29</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="17">
+        <v>150</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="18"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="16">
+        <v>31</v>
+      </c>
+      <c r="B35" s="16">
+        <v>30</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="17">
+        <v>155</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F35" s="18"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+    </row>
+    <row r="36" s="2" customFormat="1" spans="1:9">
+      <c r="A36" s="20">
+        <v>101</v>
+      </c>
+      <c r="B36" s="20">
+        <v>0</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20">
+        <v>10</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+    </row>
+    <row r="37" s="2" customFormat="1" spans="1:9">
+      <c r="A37" s="20">
+        <v>102</v>
+      </c>
+      <c r="B37" s="20">
         <v>1</v>
       </c>
-      <c r="B5" s="11">
-        <v>0</v>
-      </c>
-      <c r="C5" s="11" t="s">
+      <c r="C37" s="20"/>
+      <c r="D37" s="20">
+        <v>15</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+    </row>
+    <row r="38" s="2" customFormat="1" spans="1:9">
+      <c r="A38" s="20">
+        <v>103</v>
+      </c>
+      <c r="B38" s="20">
+        <v>2</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20">
+        <v>20</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+    </row>
+    <row r="39" s="2" customFormat="1" spans="1:9">
+      <c r="A39" s="20">
+        <v>104</v>
+      </c>
+      <c r="B39" s="20">
+        <v>3</v>
+      </c>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20">
+        <v>25</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+    </row>
+    <row r="40" s="3" customFormat="1" spans="1:11">
+      <c r="A40" s="20">
+        <v>105</v>
+      </c>
+      <c r="B40" s="20">
+        <v>4</v>
+      </c>
+      <c r="C40" s="20"/>
+      <c r="D40" s="20">
+        <v>30</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="22"/>
+      <c r="K40" s="2"/>
+    </row>
+    <row r="41" s="3" customFormat="1" spans="1:11">
+      <c r="A41" s="20">
+        <v>106</v>
+      </c>
+      <c r="B41" s="20">
+        <v>5</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20">
+        <v>35</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="22"/>
+      <c r="K41" s="2"/>
+    </row>
+    <row r="42" s="3" customFormat="1" spans="1:11">
+      <c r="A42" s="20">
+        <v>107</v>
+      </c>
+      <c r="B42" s="20">
+        <v>6</v>
+      </c>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20">
+        <v>40</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="22"/>
+      <c r="K42" s="2"/>
+    </row>
+    <row r="43" s="3" customFormat="1" spans="1:11">
+      <c r="A43" s="20">
+        <v>108</v>
+      </c>
+      <c r="B43" s="20">
+        <v>7</v>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20">
+        <v>45</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="22"/>
+      <c r="K43" s="2"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="20">
+        <v>109</v>
+      </c>
+      <c r="B44" s="20">
+        <v>8</v>
+      </c>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20">
+        <v>50</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="20">
+        <v>110</v>
+      </c>
+      <c r="B45" s="20">
+        <v>9</v>
+      </c>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20">
+        <v>55</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" customFormat="1" spans="1:11">
+      <c r="A46" s="20">
+        <v>111</v>
+      </c>
+      <c r="B46" s="20">
+        <v>10</v>
+      </c>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20">
+        <v>60</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="6"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" s="3" customFormat="1" spans="1:11">
+      <c r="A47" s="20">
+        <v>112</v>
+      </c>
+      <c r="B47" s="20">
         <v>11</v>
       </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:7">
-      <c r="A6" s="11">
-        <v>2</v>
-      </c>
-      <c r="B6" s="11">
-        <v>1</v>
-      </c>
-      <c r="C6" s="11" t="s">
+      <c r="C47" s="20"/>
+      <c r="D47" s="20">
+        <v>65</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="22"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" s="3" customFormat="1" spans="1:11">
+      <c r="A48" s="20">
+        <v>113</v>
+      </c>
+      <c r="B48" s="20">
         <v>12</v>
       </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:7">
-      <c r="A7" s="11">
-        <v>3</v>
-      </c>
-      <c r="B7" s="11">
-        <v>2</v>
-      </c>
-      <c r="C7" s="11" t="s">
+      <c r="C48" s="20"/>
+      <c r="D48" s="20">
+        <v>70</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="22"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" s="3" customFormat="1" spans="1:11">
+      <c r="A49" s="20">
+        <v>114</v>
+      </c>
+      <c r="B49" s="20">
         <v>13</v>
       </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:7">
-      <c r="A8" s="11">
-        <v>4</v>
-      </c>
-      <c r="B8" s="11">
-        <v>3</v>
-      </c>
-      <c r="C8" s="11" t="s">
+      <c r="C49" s="20"/>
+      <c r="D49" s="20">
+        <v>75</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="22"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" s="3" customFormat="1" spans="1:11">
+      <c r="A50" s="20">
+        <v>115</v>
+      </c>
+      <c r="B50" s="20">
         <v>14</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-    </row>
-    <row r="9" s="3" customFormat="1" spans="1:9">
-      <c r="A9" s="11">
-        <v>5</v>
-      </c>
-      <c r="B9" s="11">
-        <v>4</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="I9" s="2"/>
-    </row>
-    <row r="10" s="3" customFormat="1" spans="1:9">
-      <c r="A10" s="11">
-        <v>6</v>
-      </c>
-      <c r="B10" s="11">
-        <v>5</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="14"/>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" s="3" customFormat="1" spans="1:9">
-      <c r="A11" s="11">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11">
-        <v>6</v>
-      </c>
-      <c r="C11" s="11" t="s">
+      <c r="C50" s="20"/>
+      <c r="D50" s="20">
+        <v>80</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="22"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" s="3" customFormat="1" spans="1:11">
+      <c r="A51" s="20">
+        <v>116</v>
+      </c>
+      <c r="B51" s="20">
+        <v>15</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="20">
+        <v>85</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="20">
+        <v>117</v>
+      </c>
+      <c r="B52" s="20">
+        <v>16</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20">
+        <v>90</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:9">
+      <c r="A53" s="20">
+        <v>118</v>
+      </c>
+      <c r="B53" s="20">
         <v>17</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
-      <c r="I11" s="2"/>
-    </row>
-    <row r="12" s="3" customFormat="1" spans="1:9">
-      <c r="A12" s="11">
-        <v>8</v>
-      </c>
-      <c r="B12" s="11">
-        <v>7</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="C53" s="20"/>
+      <c r="D53" s="20">
+        <v>95</v>
+      </c>
+      <c r="E53" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G53" s="19"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="22"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:9">
+      <c r="A54" s="20">
+        <v>119</v>
+      </c>
+      <c r="B54" s="20">
         <v>18</v>
       </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="14"/>
-      <c r="I12" s="2"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="11">
-        <v>9</v>
-      </c>
-      <c r="B13" s="11">
-        <v>8</v>
-      </c>
-      <c r="C13" s="11" t="s">
+      <c r="C54" s="20"/>
+      <c r="D54" s="20">
+        <v>100</v>
+      </c>
+      <c r="E54" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="22"/>
+    </row>
+    <row r="55" s="3" customFormat="1" spans="1:9">
+      <c r="A55" s="20">
+        <v>120</v>
+      </c>
+      <c r="B55" s="20">
         <v>19</v>
       </c>
-      <c r="D13" s="12"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="I13" s="2"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="11">
-        <v>10</v>
-      </c>
-      <c r="B14" s="11">
-        <v>9</v>
-      </c>
-      <c r="C14" s="11" t="s">
+      <c r="C55" s="20"/>
+      <c r="D55" s="20">
+        <v>105</v>
+      </c>
+      <c r="E55" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G55" s="19"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="22"/>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:9">
+      <c r="A56" s="20">
+        <v>121</v>
+      </c>
+      <c r="B56" s="20">
         <v>20</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" customFormat="1" spans="1:9">
-      <c r="A15" s="11">
-        <v>11</v>
-      </c>
-      <c r="B15" s="11">
-        <v>10</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="C56" s="20"/>
+      <c r="D56" s="20">
+        <v>110</v>
+      </c>
+      <c r="E56" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G56" s="19"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="22"/>
+    </row>
+    <row r="57" s="3" customFormat="1" spans="1:9">
+      <c r="A57" s="20">
+        <v>122</v>
+      </c>
+      <c r="B57" s="20">
         <v>21</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="5"/>
-      <c r="I15" s="2"/>
-    </row>
-    <row r="16" s="3" customFormat="1" spans="1:9">
-      <c r="A16" s="11">
-        <v>12</v>
-      </c>
-      <c r="B16" s="11">
-        <v>11</v>
-      </c>
-      <c r="C16" s="11" t="s">
+      <c r="C57" s="20"/>
+      <c r="D57" s="20">
+        <v>115</v>
+      </c>
+      <c r="E57" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19"/>
+      <c r="I57" s="19"/>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="20">
+        <v>123</v>
+      </c>
+      <c r="B58" s="20">
         <v>22</v>
       </c>
-      <c r="D16" s="12"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="14"/>
-      <c r="I16" s="2"/>
-    </row>
-    <row r="17" s="3" customFormat="1" spans="1:9">
-      <c r="A17" s="11">
-        <v>13</v>
-      </c>
-      <c r="B17" s="11">
-        <v>12</v>
-      </c>
-      <c r="C17" s="11" t="s">
+      <c r="C58" s="20"/>
+      <c r="D58" s="20">
+        <v>120</v>
+      </c>
+      <c r="E58" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19"/>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="20">
+        <v>124</v>
+      </c>
+      <c r="B59" s="20">
         <v>23</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="14"/>
-      <c r="I17" s="2"/>
-    </row>
-    <row r="18" s="3" customFormat="1" spans="1:9">
-      <c r="A18" s="11">
-        <v>14</v>
-      </c>
-      <c r="B18" s="11">
-        <v>13</v>
-      </c>
-      <c r="C18" s="11" t="s">
+      <c r="C59" s="20"/>
+      <c r="D59" s="20">
+        <v>125</v>
+      </c>
+      <c r="E59" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G59" s="19"/>
+      <c r="H59" s="19"/>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="20">
+        <v>125</v>
+      </c>
+      <c r="B60" s="20">
         <v>24</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="14"/>
-      <c r="I18" s="2"/>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="1:9">
-      <c r="A19" s="11">
-        <v>15</v>
-      </c>
-      <c r="B19" s="11">
-        <v>14</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="C60" s="20"/>
+      <c r="D60" s="20">
+        <v>130</v>
+      </c>
+      <c r="E60" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G60" s="19"/>
+      <c r="H60" s="19"/>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="20">
+        <v>126</v>
+      </c>
+      <c r="B61" s="20">
         <v>25</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="14"/>
-      <c r="I19" s="2"/>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="1:9">
-      <c r="A20" s="11">
-        <v>16</v>
-      </c>
-      <c r="B20" s="11">
-        <v>15</v>
-      </c>
-      <c r="C20" s="11" t="s">
+      <c r="C61" s="20"/>
+      <c r="D61" s="20">
+        <v>135</v>
+      </c>
+      <c r="E61" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="20">
+        <v>127</v>
+      </c>
+      <c r="B62" s="20">
         <v>26</v>
       </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="I20" s="2"/>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="11">
-        <v>17</v>
-      </c>
-      <c r="B21" s="11">
-        <v>16</v>
-      </c>
-      <c r="C21" s="11" t="s">
+      <c r="C62" s="20"/>
+      <c r="D62" s="20">
+        <v>140</v>
+      </c>
+      <c r="E62" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="20">
+        <v>128</v>
+      </c>
+      <c r="B63" s="20">
         <v>27</v>
       </c>
-      <c r="D21" s="12"/>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="1:7">
-      <c r="A22" s="11">
-        <v>18</v>
-      </c>
-      <c r="B22" s="11">
-        <v>17</v>
-      </c>
-      <c r="C22" s="11" t="s">
+      <c r="C63" s="20"/>
+      <c r="D63" s="20">
+        <v>145</v>
+      </c>
+      <c r="E63" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G63" s="19"/>
+      <c r="H63" s="19"/>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="20">
+        <v>129</v>
+      </c>
+      <c r="B64" s="20">
         <v>28</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="13"/>
-      <c r="F22" s="13"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:7">
-      <c r="A23" s="11">
-        <v>19</v>
-      </c>
-      <c r="B23" s="11">
-        <v>18</v>
-      </c>
-      <c r="C23" s="11" t="s">
+      <c r="C64" s="20"/>
+      <c r="D64" s="20">
+        <v>150</v>
+      </c>
+      <c r="E64" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="19"/>
+      <c r="H64" s="19"/>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="20">
+        <v>130</v>
+      </c>
+      <c r="B65" s="20">
         <v>29</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="14"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:7">
-      <c r="A24" s="11">
-        <v>20</v>
-      </c>
-      <c r="B24" s="11">
-        <v>19</v>
-      </c>
-      <c r="C24" s="11" t="s">
+      <c r="C65" s="20"/>
+      <c r="D65" s="20">
+        <v>155</v>
+      </c>
+      <c r="E65" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G65" s="19"/>
+      <c r="H65" s="19"/>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="20">
+        <v>131</v>
+      </c>
+      <c r="B66" s="20">
         <v>30</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:7">
-      <c r="A25" s="11">
-        <v>21</v>
-      </c>
-      <c r="B25" s="11">
-        <v>20</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="12"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="14"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:7">
-      <c r="A26" s="11">
-        <v>22</v>
-      </c>
-      <c r="B26" s="11">
-        <v>21</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="12"/>
-      <c r="E26" s="13"/>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="11">
-        <v>23</v>
-      </c>
-      <c r="B27" s="11">
-        <v>22</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="12"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="11">
-        <v>24</v>
-      </c>
-      <c r="B28" s="11">
-        <v>23</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="11">
-        <v>25</v>
-      </c>
-      <c r="B29" s="11">
-        <v>24</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="12"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30" s="11">
-        <v>26</v>
-      </c>
-      <c r="B30" s="11">
-        <v>25</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D30" s="12"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="11">
-        <v>27</v>
-      </c>
-      <c r="B31" s="11">
-        <v>26</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D31" s="12"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="11">
-        <v>28</v>
-      </c>
-      <c r="B32" s="11">
-        <v>27</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="11">
-        <v>29</v>
-      </c>
-      <c r="B33" s="11">
-        <v>28</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34" s="11">
-        <v>30</v>
-      </c>
-      <c r="B34" s="11">
-        <v>29</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="11">
-        <v>31</v>
-      </c>
-      <c r="B35" s="11">
-        <v>30</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D35" s="12"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-    </row>
-    <row r="36" s="2" customFormat="1" spans="1:7">
-      <c r="A36" s="15">
-        <v>101</v>
-      </c>
-      <c r="B36" s="15">
-        <v>0</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:7">
-      <c r="A37" s="15">
-        <v>102</v>
-      </c>
-      <c r="B37" s="15">
-        <v>1</v>
-      </c>
-      <c r="C37" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D37" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-    </row>
-    <row r="38" s="2" customFormat="1" spans="1:7">
-      <c r="A38" s="15">
-        <v>103</v>
-      </c>
-      <c r="B38" s="15">
-        <v>2</v>
-      </c>
-      <c r="C38" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D38" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-    </row>
-    <row r="39" s="2" customFormat="1" spans="1:7">
-      <c r="A39" s="15">
-        <v>104</v>
-      </c>
-      <c r="B39" s="15">
-        <v>3</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-    </row>
-    <row r="40" s="3" customFormat="1" spans="1:9">
-      <c r="A40" s="15">
-        <v>105</v>
-      </c>
-      <c r="B40" s="15">
-        <v>4</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D40" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="14"/>
-      <c r="I40" s="2"/>
-    </row>
-    <row r="41" s="3" customFormat="1" spans="1:9">
-      <c r="A41" s="15">
-        <v>106</v>
-      </c>
-      <c r="B41" s="15">
-        <v>5</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="14"/>
-      <c r="I41" s="2"/>
-    </row>
-    <row r="42" s="3" customFormat="1" spans="1:9">
-      <c r="A42" s="15">
-        <v>107</v>
-      </c>
-      <c r="B42" s="15">
-        <v>6</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="14"/>
-      <c r="I42" s="2"/>
-    </row>
-    <row r="43" s="3" customFormat="1" spans="1:9">
-      <c r="A43" s="15">
-        <v>108</v>
-      </c>
-      <c r="B43" s="15">
-        <v>7</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="D43" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="14"/>
-      <c r="I43" s="2"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="15">
-        <v>109</v>
-      </c>
-      <c r="B44" s="15">
-        <v>8</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="I44" s="2"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="15">
-        <v>110</v>
-      </c>
-      <c r="B45" s="15">
-        <v>9</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="I45" s="2"/>
-    </row>
-    <row r="46" customFormat="1" spans="1:9">
-      <c r="A46" s="15">
-        <v>111</v>
-      </c>
-      <c r="B46" s="15">
-        <v>10</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="D46" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="5"/>
-      <c r="I46" s="2"/>
-    </row>
-    <row r="47" s="3" customFormat="1" spans="1:9">
-      <c r="A47" s="15">
-        <v>112</v>
-      </c>
-      <c r="B47" s="15">
-        <v>11</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="D47" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="14"/>
-      <c r="I47" s="2"/>
-    </row>
-    <row r="48" s="3" customFormat="1" spans="1:9">
-      <c r="A48" s="15">
-        <v>113</v>
-      </c>
-      <c r="B48" s="15">
-        <v>12</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D48" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="14"/>
-      <c r="I48" s="2"/>
-    </row>
-    <row r="49" s="3" customFormat="1" spans="1:9">
-      <c r="A49" s="15">
-        <v>114</v>
-      </c>
-      <c r="B49" s="15">
-        <v>13</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="14"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" s="3" customFormat="1" spans="1:9">
-      <c r="A50" s="15">
-        <v>115</v>
-      </c>
-      <c r="B50" s="15">
-        <v>14</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D50" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="14"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" s="3" customFormat="1" spans="1:9">
-      <c r="A51" s="15">
-        <v>116</v>
-      </c>
-      <c r="B51" s="15">
-        <v>15</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="13"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" s="15">
-        <v>117</v>
-      </c>
-      <c r="B52" s="15">
-        <v>16</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D52" s="16">
-        <v>45931</v>
-      </c>
-    </row>
-    <row r="53" s="3" customFormat="1" spans="1:7">
-      <c r="A53" s="15">
-        <v>118</v>
-      </c>
-      <c r="B53" s="15">
-        <v>17</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="14"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:7">
-      <c r="A54" s="15">
-        <v>119</v>
-      </c>
-      <c r="B54" s="15">
-        <v>18</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D54" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="14"/>
-    </row>
-    <row r="55" s="3" customFormat="1" spans="1:7">
-      <c r="A55" s="15">
-        <v>120</v>
-      </c>
-      <c r="B55" s="15">
-        <v>19</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="D55" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="14"/>
-    </row>
-    <row r="56" s="3" customFormat="1" spans="1:7">
-      <c r="A56" s="15">
-        <v>121</v>
-      </c>
-      <c r="B56" s="15">
-        <v>20</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="14"/>
-    </row>
-    <row r="57" s="3" customFormat="1" spans="1:7">
-      <c r="A57" s="15">
-        <v>122</v>
-      </c>
-      <c r="B57" s="15">
-        <v>21</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="13"/>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58" s="15">
-        <v>123</v>
-      </c>
-      <c r="B58" s="15">
-        <v>22</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59" s="15">
-        <v>124</v>
-      </c>
-      <c r="B59" s="15">
-        <v>23</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D59" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60" s="15">
-        <v>125</v>
-      </c>
-      <c r="B60" s="15">
-        <v>24</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="15">
-        <v>126</v>
-      </c>
-      <c r="B61" s="15">
-        <v>25</v>
-      </c>
-      <c r="C61" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D61" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="15">
-        <v>127</v>
-      </c>
-      <c r="B62" s="15">
-        <v>26</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D62" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="15">
-        <v>128</v>
-      </c>
-      <c r="B63" s="15">
-        <v>27</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="D63" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="15">
-        <v>129</v>
-      </c>
-      <c r="B64" s="15">
-        <v>28</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65" s="15">
-        <v>130</v>
-      </c>
-      <c r="B65" s="15">
-        <v>29</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D65" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66" s="15">
-        <v>131</v>
-      </c>
-      <c r="B66" s="15">
-        <v>30</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D66" s="16">
-        <v>45931</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
+      <c r="C66" s="20"/>
+      <c r="D66" s="20">
+        <v>160</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="G66" s="19"/>
+      <c r="H66" s="19"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/PointsAwardSignin.xlsx
+++ b/poker/resources/sample/PointsAwardSignin.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="17">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>15</v>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="17">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>15</v>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="17">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>15</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="17">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>15</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="17">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>15</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="17">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>15</v>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="17">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>15</v>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>15</v>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="17">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>15</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="17">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>15</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="17">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>15</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="17">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>15</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="17">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>15</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="17">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>15</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="17">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>15</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="17">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>15</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="17">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>15</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="17">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>15</v>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="17">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>15</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="17">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>15</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="17">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>15</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="17">
-        <v>110</v>
+        <v>17</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>15</v>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="17">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>15</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="17">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>15</v>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="17">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>15</v>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="17">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>15</v>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="17">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>15</v>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="17">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>15</v>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="17">
-        <v>145</v>
+        <v>22</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>15</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="17">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>15</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="17">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>15</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="C36" s="20"/>
       <c r="D36" s="20">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E36" s="20" t="s">
         <v>15</v>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="20">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E37" s="20" t="s">
         <v>15</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="20">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E38" s="20" t="s">
         <v>15</v>
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="20">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E39" s="20" t="s">
         <v>15</v>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C40" s="20"/>
       <c r="D40" s="20">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="E40" s="20" t="s">
         <v>15</v>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="20">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="E41" s="20" t="s">
         <v>15</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="C42" s="20"/>
       <c r="D42" s="20">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="E42" s="20" t="s">
         <v>15</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="20">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E43" s="20" t="s">
         <v>15</v>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="20">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="E44" s="20" t="s">
         <v>15</v>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="20">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="E45" s="20" t="s">
         <v>15</v>
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="20">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="E46" s="20" t="s">
         <v>15</v>
@@ -2195,7 +2195,7 @@
       </c>
       <c r="C47" s="20"/>
       <c r="D47" s="20">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="E47" s="20" t="s">
         <v>15</v>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C48" s="20"/>
       <c r="D48" s="20">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="E48" s="20" t="s">
         <v>15</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C49" s="20"/>
       <c r="D49" s="20">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E49" s="20" t="s">
         <v>15</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="20">
-        <v>80</v>
+        <v>13</v>
       </c>
       <c r="E50" s="20" t="s">
         <v>15</v>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="20">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="E51" s="20" t="s">
         <v>15</v>
@@ -2305,7 +2305,7 @@
       </c>
       <c r="C52" s="20"/>
       <c r="D52" s="20">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="E52" s="20" t="s">
         <v>15</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="20">
-        <v>95</v>
+        <v>15</v>
       </c>
       <c r="E53" s="20" t="s">
         <v>15</v>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="20">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="E54" s="20" t="s">
         <v>15</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="20">
-        <v>105</v>
+        <v>15</v>
       </c>
       <c r="E55" s="20" t="s">
         <v>15</v>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="20">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="E56" s="20" t="s">
         <v>15</v>
@@ -2407,7 +2407,7 @@
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="20">
-        <v>115</v>
+        <v>17</v>
       </c>
       <c r="E57" s="20" t="s">
         <v>15</v>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="20">
-        <v>120</v>
+        <v>17</v>
       </c>
       <c r="E58" s="20" t="s">
         <v>15</v>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="C59" s="20"/>
       <c r="D59" s="20">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c r="E59" s="20" t="s">
         <v>15</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="20">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="E60" s="20" t="s">
         <v>15</v>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="C61" s="20"/>
       <c r="D61" s="20">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E61" s="20" t="s">
         <v>15</v>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C62" s="20"/>
       <c r="D62" s="20">
-        <v>140</v>
+        <v>19</v>
       </c>
       <c r="E62" s="20" t="s">
         <v>15</v>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="C63" s="20"/>
       <c r="D63" s="20">
-        <v>145</v>
+        <v>19</v>
       </c>
       <c r="E63" s="20" t="s">
         <v>15</v>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="C64" s="20"/>
       <c r="D64" s="20">
-        <v>150</v>
+        <v>22</v>
       </c>
       <c r="E64" s="20" t="s">
         <v>15</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C65" s="20"/>
       <c r="D65" s="20">
-        <v>155</v>
+        <v>22</v>
       </c>
       <c r="E65" s="20" t="s">
         <v>15</v>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="C66" s="20"/>
       <c r="D66" s="20">
-        <v>160</v>
+        <v>22</v>
       </c>
       <c r="E66" s="20" t="s">
         <v>15</v>

--- a/poker/resources/sample/PointsAwardSignin.xlsx
+++ b/poker/resources/sample/PointsAwardSignin.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="PointsAwardSignin" sheetId="1" r:id="rId1"/>
@@ -395,12 +395,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -935,13 +935,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1295,7 +1295,7 @@
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:11">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:11">
       <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:11">
       <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:11">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1363,7 +1363,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="11"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:9">
+    <row r="5" s="2" customFormat="1" spans="1:11">
       <c r="A5" s="16">
         <v>1</v>
       </c>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E5" s="17" t="s">
         <v>15</v>
@@ -1382,7 +1382,7 @@
       <c r="H5" s="19"/>
       <c r="I5" s="19"/>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:9">
+    <row r="6" s="2" customFormat="1" spans="1:11">
       <c r="A6" s="16">
         <v>2</v>
       </c>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="C6" s="16"/>
       <c r="D6" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E6" s="17" t="s">
         <v>15</v>
@@ -1401,7 +1401,7 @@
       <c r="H6" s="19"/>
       <c r="I6" s="19"/>
     </row>
-    <row r="7" s="2" customFormat="1" spans="1:9">
+    <row r="7" s="2" customFormat="1" spans="1:11">
       <c r="A7" s="16">
         <v>3</v>
       </c>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" s="17" t="s">
         <v>15</v>
@@ -1420,7 +1420,7 @@
       <c r="H7" s="19"/>
       <c r="I7" s="19"/>
     </row>
-    <row r="8" s="2" customFormat="1" spans="1:9">
+    <row r="8" s="2" customFormat="1" spans="1:11">
       <c r="A8" s="16">
         <v>4</v>
       </c>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C8" s="16"/>
       <c r="D8" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" s="17" t="s">
         <v>15</v>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E9" s="17" t="s">
         <v>15</v>
@@ -1456,7 +1456,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
-      <c r="I9" s="22"/>
+      <c r="I9" s="20"/>
       <c r="K9" s="2"/>
     </row>
     <row r="10" s="3" customFormat="1" spans="1:11">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="C10" s="16"/>
       <c r="D10" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E10" s="17" t="s">
         <v>15</v>
@@ -1476,7 +1476,7 @@
       <c r="F10" s="18"/>
       <c r="G10" s="19"/>
       <c r="H10" s="19"/>
-      <c r="I10" s="22"/>
+      <c r="I10" s="20"/>
       <c r="K10" s="2"/>
     </row>
     <row r="11" s="3" customFormat="1" spans="1:11">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>15</v>
@@ -1496,7 +1496,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
-      <c r="I11" s="22"/>
+      <c r="I11" s="20"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12" s="3" customFormat="1" spans="1:11">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E12" s="17" t="s">
         <v>15</v>
@@ -1516,7 +1516,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="20"/>
       <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C13" s="16"/>
       <c r="D13" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E13" s="17" t="s">
         <v>15</v>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E14" s="17" t="s">
         <v>15</v>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E15" s="17" t="s">
         <v>15</v>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C16" s="16"/>
       <c r="D16" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E16" s="17" t="s">
         <v>15</v>
@@ -1594,7 +1594,7 @@
       <c r="F16" s="18"/>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="22"/>
+      <c r="I16" s="20"/>
       <c r="K16" s="2"/>
     </row>
     <row r="17" s="3" customFormat="1" spans="1:11">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>15</v>
@@ -1614,7 +1614,7 @@
       <c r="F17" s="18"/>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="22"/>
+      <c r="I17" s="20"/>
       <c r="K17" s="2"/>
     </row>
     <row r="18" s="3" customFormat="1" spans="1:11">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C18" s="16"/>
       <c r="D18" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>15</v>
@@ -1634,7 +1634,7 @@
       <c r="F18" s="18"/>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
-      <c r="I18" s="22"/>
+      <c r="I18" s="20"/>
       <c r="K18" s="2"/>
     </row>
     <row r="19" s="3" customFormat="1" spans="1:11">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>15</v>
@@ -1654,7 +1654,7 @@
       <c r="F19" s="18"/>
       <c r="G19" s="19"/>
       <c r="H19" s="19"/>
-      <c r="I19" s="22"/>
+      <c r="I19" s="20"/>
       <c r="K19" s="2"/>
     </row>
     <row r="20" s="3" customFormat="1" spans="1:11">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E20" s="17" t="s">
         <v>15</v>
@@ -1677,7 +1677,7 @@
       <c r="I20" s="19"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:11">
       <c r="A21" s="16">
         <v>17</v>
       </c>
@@ -1686,14 +1686,14 @@
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="E21" s="17" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="18"/>
     </row>
-    <row r="22" s="3" customFormat="1" spans="1:9">
+    <row r="22" s="3" customFormat="1" spans="1:11">
       <c r="A22" s="16">
         <v>18</v>
       </c>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E22" s="17" t="s">
         <v>15</v>
@@ -1710,9 +1710,9 @@
       <c r="F22" s="18"/>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
-      <c r="I22" s="22"/>
-    </row>
-    <row r="23" s="3" customFormat="1" spans="1:9">
+      <c r="I22" s="20"/>
+    </row>
+    <row r="23" s="3" customFormat="1" spans="1:11">
       <c r="A23" s="16">
         <v>19</v>
       </c>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E23" s="17" t="s">
         <v>15</v>
@@ -1729,9 +1729,9 @@
       <c r="F23" s="18"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
-      <c r="I23" s="22"/>
-    </row>
-    <row r="24" s="3" customFormat="1" spans="1:9">
+      <c r="I23" s="20"/>
+    </row>
+    <row r="24" s="3" customFormat="1" spans="1:11">
       <c r="A24" s="16">
         <v>20</v>
       </c>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>15</v>
@@ -1748,9 +1748,9 @@
       <c r="F24" s="18"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
-      <c r="I24" s="22"/>
-    </row>
-    <row r="25" s="3" customFormat="1" spans="1:9">
+      <c r="I24" s="20"/>
+    </row>
+    <row r="25" s="3" customFormat="1" spans="1:11">
       <c r="A25" s="16">
         <v>21</v>
       </c>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="C25" s="16"/>
       <c r="D25" s="17">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E25" s="17" t="s">
         <v>15</v>
@@ -1767,9 +1767,9 @@
       <c r="F25" s="18"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
-      <c r="I25" s="22"/>
-    </row>
-    <row r="26" s="3" customFormat="1" spans="1:9">
+      <c r="I25" s="20"/>
+    </row>
+    <row r="26" s="3" customFormat="1" spans="1:11">
       <c r="A26" s="16">
         <v>22</v>
       </c>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="17">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E26" s="17" t="s">
         <v>15</v>
@@ -1788,7 +1788,7 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:11">
       <c r="A27" s="16">
         <v>23</v>
       </c>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="17">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E27" s="17" t="s">
         <v>15</v>
@@ -1806,7 +1806,7 @@
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:11">
       <c r="A28" s="16">
         <v>24</v>
       </c>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="17">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>15</v>
@@ -1824,7 +1824,7 @@
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:11">
       <c r="A29" s="16">
         <v>25</v>
       </c>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="17">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E29" s="17" t="s">
         <v>15</v>
@@ -1842,7 +1842,7 @@
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:11">
       <c r="A30" s="16">
         <v>26</v>
       </c>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="C30" s="16"/>
       <c r="D30" s="17">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E30" s="17" t="s">
         <v>15</v>
@@ -1860,7 +1860,7 @@
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:11">
       <c r="A31" s="16">
         <v>27</v>
       </c>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="17">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E31" s="17" t="s">
         <v>15</v>
@@ -1878,7 +1878,7 @@
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:11">
       <c r="A32" s="16">
         <v>28</v>
       </c>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="17">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>15</v>
@@ -1896,7 +1896,7 @@
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:11">
       <c r="A33" s="16">
         <v>29</v>
       </c>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="C33" s="16"/>
       <c r="D33" s="17">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E33" s="17" t="s">
         <v>15</v>
@@ -1914,7 +1914,7 @@
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:11">
       <c r="A34" s="16">
         <v>30</v>
       </c>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="17">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E34" s="17" t="s">
         <v>15</v>
@@ -1932,7 +1932,7 @@
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:11">
       <c r="A35" s="16">
         <v>31</v>
       </c>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="17">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E35" s="17" t="s">
         <v>15</v>
@@ -1950,84 +1950,84 @@
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
     </row>
-    <row r="36" s="2" customFormat="1" spans="1:9">
-      <c r="A36" s="20">
+    <row r="36" s="2" customFormat="1" spans="1:11">
+      <c r="A36" s="21">
         <v>101</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="21">
         <v>0</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20">
-        <v>4</v>
-      </c>
-      <c r="E36" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="21" t="s">
+      <c r="C36" s="21"/>
+      <c r="D36" s="21">
+        <v>8</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
     </row>
-    <row r="37" s="2" customFormat="1" spans="1:9">
-      <c r="A37" s="20">
+    <row r="37" s="2" customFormat="1" spans="1:11">
+      <c r="A37" s="21">
         <v>102</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="21">
         <v>1</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20">
-        <v>4</v>
-      </c>
-      <c r="E37" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="21" t="s">
+      <c r="C37" s="21"/>
+      <c r="D37" s="21">
+        <v>8</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F37" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
     </row>
-    <row r="38" s="2" customFormat="1" spans="1:9">
-      <c r="A38" s="20">
+    <row r="38" s="2" customFormat="1" spans="1:11">
+      <c r="A38" s="21">
         <v>103</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="21">
         <v>2</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20">
-        <v>4</v>
-      </c>
-      <c r="E38" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="21" t="s">
+      <c r="C38" s="21"/>
+      <c r="D38" s="21">
+        <v>8</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F38" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
     </row>
-    <row r="39" s="2" customFormat="1" spans="1:9">
-      <c r="A39" s="20">
+    <row r="39" s="2" customFormat="1" spans="1:11">
+      <c r="A39" s="21">
         <v>104</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="21">
         <v>3</v>
       </c>
-      <c r="C39" s="20"/>
-      <c r="D39" s="20">
-        <v>6</v>
-      </c>
-      <c r="E39" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="21" t="s">
+      <c r="C39" s="21"/>
+      <c r="D39" s="21">
+        <v>11</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G39" s="19"/>
@@ -2035,108 +2035,108 @@
       <c r="I39" s="19"/>
     </row>
     <row r="40" s="3" customFormat="1" spans="1:11">
-      <c r="A40" s="20">
+      <c r="A40" s="21">
         <v>105</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="21">
         <v>4</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20">
-        <v>6</v>
-      </c>
-      <c r="E40" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F40" s="21" t="s">
+      <c r="C40" s="21"/>
+      <c r="D40" s="21">
+        <v>11</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F40" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
-      <c r="I40" s="22"/>
+      <c r="I40" s="20"/>
       <c r="K40" s="2"/>
     </row>
     <row r="41" s="3" customFormat="1" spans="1:11">
-      <c r="A41" s="20">
+      <c r="A41" s="21">
         <v>106</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="21">
         <v>5</v>
       </c>
-      <c r="C41" s="20"/>
-      <c r="D41" s="20">
-        <v>6</v>
-      </c>
-      <c r="E41" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="21" t="s">
+      <c r="C41" s="21"/>
+      <c r="D41" s="21">
+        <v>11</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
-      <c r="I41" s="22"/>
+      <c r="I41" s="20"/>
       <c r="K41" s="2"/>
     </row>
     <row r="42" s="3" customFormat="1" spans="1:11">
-      <c r="A42" s="20">
+      <c r="A42" s="21">
         <v>107</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="21">
         <v>6</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20">
-        <v>6</v>
-      </c>
-      <c r="E42" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F42" s="21" t="s">
+      <c r="C42" s="21"/>
+      <c r="D42" s="21">
+        <v>11</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
-      <c r="I42" s="22"/>
+      <c r="I42" s="20"/>
       <c r="K42" s="2"/>
     </row>
     <row r="43" s="3" customFormat="1" spans="1:11">
-      <c r="A43" s="20">
+      <c r="A43" s="21">
         <v>108</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="21">
         <v>7</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20">
-        <v>9</v>
-      </c>
-      <c r="E43" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="21" t="s">
+      <c r="C43" s="21"/>
+      <c r="D43" s="21">
+        <v>15</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F43" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
-      <c r="I43" s="22"/>
+      <c r="I43" s="20"/>
       <c r="K43" s="2"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="20">
+      <c r="A44" s="21">
         <v>109</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="21">
         <v>8</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20">
-        <v>9</v>
-      </c>
-      <c r="E44" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F44" s="21" t="s">
+      <c r="C44" s="21"/>
+      <c r="D44" s="21">
+        <v>15</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G44" s="19"/>
@@ -2144,20 +2144,20 @@
       <c r="K44" s="2"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="20">
+      <c r="A45" s="21">
         <v>110</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="21">
         <v>9</v>
       </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20">
-        <v>9</v>
-      </c>
-      <c r="E45" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F45" s="21" t="s">
+      <c r="C45" s="21"/>
+      <c r="D45" s="21">
+        <v>15</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F45" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G45" s="19"/>
@@ -2165,20 +2165,20 @@
       <c r="K45" s="2"/>
     </row>
     <row r="46" customFormat="1" spans="1:11">
-      <c r="A46" s="20">
+      <c r="A46" s="21">
         <v>111</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="21">
         <v>10</v>
       </c>
-      <c r="C46" s="20"/>
-      <c r="D46" s="20">
-        <v>11</v>
-      </c>
-      <c r="E46" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F46" s="21" t="s">
+      <c r="C46" s="21"/>
+      <c r="D46" s="21">
+        <v>19</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F46" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G46" s="19"/>
@@ -2187,108 +2187,108 @@
       <c r="K46" s="2"/>
     </row>
     <row r="47" s="3" customFormat="1" spans="1:11">
-      <c r="A47" s="20">
+      <c r="A47" s="21">
         <v>112</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="21">
         <v>11</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20">
-        <v>11</v>
-      </c>
-      <c r="E47" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" s="21" t="s">
+      <c r="C47" s="21"/>
+      <c r="D47" s="21">
+        <v>19</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F47" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G47" s="19"/>
       <c r="H47" s="19"/>
-      <c r="I47" s="22"/>
+      <c r="I47" s="20"/>
       <c r="K47" s="2"/>
     </row>
     <row r="48" s="3" customFormat="1" spans="1:11">
-      <c r="A48" s="20">
+      <c r="A48" s="21">
         <v>113</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="21">
         <v>12</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20">
-        <v>11</v>
-      </c>
-      <c r="E48" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" s="21" t="s">
+      <c r="C48" s="21"/>
+      <c r="D48" s="21">
+        <v>19</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G48" s="19"/>
       <c r="H48" s="19"/>
-      <c r="I48" s="22"/>
+      <c r="I48" s="20"/>
       <c r="K48" s="2"/>
     </row>
     <row r="49" s="3" customFormat="1" spans="1:11">
-      <c r="A49" s="20">
+      <c r="A49" s="21">
         <v>114</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="21">
         <v>13</v>
       </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20">
-        <v>11</v>
-      </c>
-      <c r="E49" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="21" t="s">
+      <c r="C49" s="21"/>
+      <c r="D49" s="21">
+        <v>19</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F49" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G49" s="19"/>
       <c r="H49" s="19"/>
-      <c r="I49" s="22"/>
+      <c r="I49" s="20"/>
       <c r="K49" s="2"/>
     </row>
     <row r="50" s="3" customFormat="1" spans="1:11">
-      <c r="A50" s="20">
+      <c r="A50" s="21">
         <v>115</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="21">
         <v>14</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20">
-        <v>13</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="21" t="s">
+      <c r="C50" s="21"/>
+      <c r="D50" s="21">
+        <v>23</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G50" s="19"/>
       <c r="H50" s="19"/>
-      <c r="I50" s="22"/>
+      <c r="I50" s="20"/>
       <c r="K50" s="2"/>
     </row>
     <row r="51" s="3" customFormat="1" spans="1:11">
-      <c r="A51" s="20">
+      <c r="A51" s="21">
         <v>116</v>
       </c>
-      <c r="B51" s="20">
-        <v>15</v>
-      </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20">
-        <v>13</v>
-      </c>
-      <c r="E51" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="21" t="s">
+      <c r="B51" s="21">
+        <v>15</v>
+      </c>
+      <c r="C51" s="21"/>
+      <c r="D51" s="21">
+        <v>23</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G51" s="19"/>
@@ -2296,304 +2296,304 @@
       <c r="I51" s="19"/>
       <c r="K51" s="2"/>
     </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="20">
+    <row r="52" spans="1:11">
+      <c r="A52" s="21">
         <v>117</v>
       </c>
-      <c r="B52" s="20">
-        <v>16</v>
-      </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20">
-        <v>13</v>
-      </c>
-      <c r="E52" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" s="3" customFormat="1" spans="1:9">
-      <c r="A53" s="20">
+      <c r="B52" s="21">
+        <v>16</v>
+      </c>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21">
+        <v>23</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="53" s="3" customFormat="1" spans="1:11">
+      <c r="A53" s="21">
         <v>118</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="21">
         <v>17</v>
       </c>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20">
-        <v>15</v>
-      </c>
-      <c r="E53" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="21" t="s">
+      <c r="C53" s="21"/>
+      <c r="D53" s="21">
+        <v>26</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F53" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G53" s="19"/>
       <c r="H53" s="19"/>
-      <c r="I53" s="22"/>
-    </row>
-    <row r="54" s="3" customFormat="1" spans="1:9">
-      <c r="A54" s="20">
+      <c r="I53" s="20"/>
+    </row>
+    <row r="54" s="3" customFormat="1" spans="1:11">
+      <c r="A54" s="21">
         <v>119</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="21">
         <v>18</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20">
-        <v>15</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="21" t="s">
+      <c r="C54" s="21"/>
+      <c r="D54" s="21">
+        <v>26</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F54" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G54" s="19"/>
       <c r="H54" s="19"/>
-      <c r="I54" s="22"/>
-    </row>
-    <row r="55" s="3" customFormat="1" spans="1:9">
-      <c r="A55" s="20">
+      <c r="I54" s="20"/>
+    </row>
+    <row r="55" s="3" customFormat="1" spans="1:11">
+      <c r="A55" s="21">
         <v>120</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="21">
         <v>19</v>
       </c>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20">
-        <v>15</v>
-      </c>
-      <c r="E55" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" s="21" t="s">
+      <c r="C55" s="21"/>
+      <c r="D55" s="21">
+        <v>26</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G55" s="19"/>
       <c r="H55" s="19"/>
-      <c r="I55" s="22"/>
-    </row>
-    <row r="56" s="3" customFormat="1" spans="1:9">
-      <c r="A56" s="20">
+      <c r="I55" s="20"/>
+    </row>
+    <row r="56" s="3" customFormat="1" spans="1:11">
+      <c r="A56" s="21">
         <v>121</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="21">
         <v>20</v>
       </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20">
-        <v>15</v>
-      </c>
-      <c r="E56" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" s="21" t="s">
+      <c r="C56" s="21"/>
+      <c r="D56" s="21">
+        <v>26</v>
+      </c>
+      <c r="E56" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F56" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G56" s="19"/>
       <c r="H56" s="19"/>
-      <c r="I56" s="22"/>
-    </row>
-    <row r="57" s="3" customFormat="1" spans="1:9">
-      <c r="A57" s="20">
+      <c r="I56" s="20"/>
+    </row>
+    <row r="57" s="3" customFormat="1" spans="1:11">
+      <c r="A57" s="21">
         <v>122</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="21">
         <v>21</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20">
-        <v>17</v>
-      </c>
-      <c r="E57" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="21" t="s">
+      <c r="C57" s="21"/>
+      <c r="D57" s="21">
+        <v>30</v>
+      </c>
+      <c r="E57" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G57" s="19"/>
       <c r="H57" s="19"/>
       <c r="I57" s="19"/>
     </row>
-    <row r="58" spans="1:8">
-      <c r="A58" s="20">
+    <row r="58" spans="1:11">
+      <c r="A58" s="21">
         <v>123</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="21">
         <v>22</v>
       </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20">
-        <v>17</v>
-      </c>
-      <c r="E58" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" s="21" t="s">
+      <c r="C58" s="21"/>
+      <c r="D58" s="21">
+        <v>30</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G58" s="19"/>
       <c r="H58" s="19"/>
     </row>
-    <row r="59" spans="1:8">
-      <c r="A59" s="20">
+    <row r="59" spans="1:11">
+      <c r="A59" s="21">
         <v>124</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="21">
         <v>23</v>
       </c>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20">
-        <v>17</v>
-      </c>
-      <c r="E59" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" s="21" t="s">
+      <c r="C59" s="21"/>
+      <c r="D59" s="21">
+        <v>30</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G59" s="19"/>
       <c r="H59" s="19"/>
     </row>
-    <row r="60" spans="1:8">
-      <c r="A60" s="20">
+    <row r="60" spans="1:11">
+      <c r="A60" s="21">
         <v>125</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="21">
         <v>24</v>
       </c>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20">
-        <v>19</v>
-      </c>
-      <c r="E60" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" s="21" t="s">
+      <c r="C60" s="21"/>
+      <c r="D60" s="21">
+        <v>34</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F60" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G60" s="19"/>
       <c r="H60" s="19"/>
     </row>
-    <row r="61" spans="1:8">
-      <c r="A61" s="20">
+    <row r="61" spans="1:11">
+      <c r="A61" s="21">
         <v>126</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="21">
         <v>25</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20">
-        <v>19</v>
-      </c>
-      <c r="E61" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="21" t="s">
+      <c r="C61" s="21"/>
+      <c r="D61" s="21">
+        <v>34</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F61" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="19"/>
       <c r="H61" s="19"/>
     </row>
-    <row r="62" spans="1:8">
-      <c r="A62" s="20">
+    <row r="62" spans="1:11">
+      <c r="A62" s="21">
         <v>127</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="21">
         <v>26</v>
       </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20">
-        <v>19</v>
-      </c>
-      <c r="E62" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F62" s="21" t="s">
+      <c r="C62" s="21"/>
+      <c r="D62" s="21">
+        <v>34</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F62" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G62" s="19"/>
       <c r="H62" s="19"/>
     </row>
-    <row r="63" spans="1:8">
-      <c r="A63" s="20">
+    <row r="63" spans="1:11">
+      <c r="A63" s="21">
         <v>128</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="21">
         <v>27</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20">
-        <v>19</v>
-      </c>
-      <c r="E63" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" s="21" t="s">
+      <c r="C63" s="21"/>
+      <c r="D63" s="21">
+        <v>34</v>
+      </c>
+      <c r="E63" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F63" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G63" s="19"/>
       <c r="H63" s="19"/>
     </row>
-    <row r="64" spans="1:8">
-      <c r="A64" s="20">
+    <row r="64" spans="1:11">
+      <c r="A64" s="21">
         <v>129</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="21">
         <v>28</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20">
-        <v>22</v>
-      </c>
-      <c r="E64" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" s="21" t="s">
+      <c r="C64" s="21"/>
+      <c r="D64" s="21">
+        <v>38</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G64" s="19"/>
       <c r="H64" s="19"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="20">
+      <c r="A65" s="21">
         <v>130</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="21">
         <v>29</v>
       </c>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20">
-        <v>22</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F65" s="21" t="s">
+      <c r="C65" s="21"/>
+      <c r="D65" s="21">
+        <v>38</v>
+      </c>
+      <c r="E65" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G65" s="19"/>
       <c r="H65" s="19"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="20">
+      <c r="A66" s="21">
         <v>131</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="21">
         <v>30</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20">
-        <v>22</v>
-      </c>
-      <c r="E66" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" s="21" t="s">
+      <c r="C66" s="21"/>
+      <c r="D66" s="21">
+        <v>38</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" s="22" t="s">
         <v>16</v>
       </c>
       <c r="G66" s="19"/>
